--- a/results/job_matches_2026-09-16.xlsx
+++ b/results/job_matches_2026-09-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G137"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,70 +643,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Architect - Irving,TX</t>
+          <t>Software Engineer III (Full Stack)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Sprouts Farmers Market</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe7b157eada5171</t>
+          <t>https://www.indeed.com/viewjob?jk=9717265e88692311</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III (Full Stack)</t>
+          <t>Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sprouts Farmers Market</t>
+          <t>Acxiom</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Conway, AR, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Kafka, SQL Server</t>
+          <t>AWS, S3, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9717265e88692311</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb6bc702cc8f819</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Site Reliability Engineer II - Data Platforms - Remote</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>UNFI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec87e7c5d235465</t>
+          <t>https://www.indeed.com/viewjob?jk=8613083ecb455e28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IT Site Reliability Engineer II - Data Platforms - Remote</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UNFI</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8613083ecb455e28</t>
+          <t>https://www.indeed.com/viewjob?jk=a7223f033607ba4e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Systems Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Elsevier</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7223f033607ba4e</t>
+          <t>https://www.indeed.com/viewjob?jk=93c4fe230bc9da32</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Elsevier</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c4fe230bc9da32</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a3565a4a0f6c00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a3565a4a0f6c00</t>
+          <t>https://www.indeed.com/viewjob?jk=56823350b0e43e7b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Dev Engineer SOW # EG CO1 B2 US</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56823350b0e43e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=d53cf9d0bf68048b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Databrick Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TradeWind Services</t>
+          <t>Concord USA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53e3a08c1c44bf91</t>
+          <t>https://www.indeed.com/viewjob?jk=962688fb52f665fe</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Sr Software Engineer - Medical Automation SaaS platform ( Python + data pipelines + automation</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Concord USA</t>
+          <t>Relentless Talent</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=962688fb52f665fe</t>
+          <t>https://www.indeed.com/viewjob?jk=3242e705b806ab21</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Medical Automation SaaS platform ( Python + data pipelines + automation</t>
+          <t>Sr Software Engineer ( Gen AI)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Relentless Talent</t>
+          <t>Blue Yonder</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3242e705b806ab21</t>
+          <t>https://www.indeed.com/viewjob?jk=9a55a27bf3bdffde</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Software Engineer ( Gen AI)</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Blue Yonder</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a55a27bf3bdffde</t>
+          <t>https://www.indeed.com/viewjob?jk=772f1be866124af1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Azure Data Architect</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7608d5894436a65d</t>
+          <t>https://www.indeed.com/viewjob?jk=52fb54968897c95b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>Senior Engineer I, DevOps</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CareMetx, LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fb54968897c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b79178087231c2</t>
         </is>
       </c>
     </row>
@@ -1238,25 +1238,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Engineer I, DevOps</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CareMetx, LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b79178087231c2</t>
+          <t>https://www.indeed.com/viewjob?jk=463e1932681d1ea9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463e1932681d1ea9</t>
+          <t>https://www.indeed.com/viewjob?jk=0520916947bccd63</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Site Reliability Engineer - GCP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Veson Nautical</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0520916947bccd63</t>
+          <t>https://www.indeed.com/viewjob?jk=9c626e90462e462c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>isolved</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca46288b741312f0</t>
+          <t>https://www.indeed.com/viewjob?jk=8b45e4d16b1cb423</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>isolved</t>
+          <t>Mike Albert Leasing, Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b45e4d16b1cb423</t>
+          <t>https://www.indeed.com/viewjob?jk=28ad3074a940aca6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mike Albert Leasing, Inc</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ad3074a940aca6</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca57e502d5a7eb</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>2026016 - Software Engineer II (CA)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Moline, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca57e502d5a7eb</t>
+          <t>https://www.indeed.com/viewjob?jk=5f2f62beea8bb80a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026016 - Software Engineer II (CA)</t>
+          <t>Trading Analytics Developer, Quantitative Trading</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>CRYPTO.com</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Moline, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f2f62beea8bb80a</t>
+          <t>https://www.indeed.com/viewjob?jk=2cfb2225c982e0d3</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfb2225c982e0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=be62e17c354b320c</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,42 +1581,42 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be62e17c354b320c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c35d0114447fb50</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Trading Analytics Developer, Quantitative Trading</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CRYPTO.com</t>
+          <t>Aeroflow Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Asheville, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, MongoDB, ETL, CI/CD</t>
+          <t>AWS, Glue, Athena, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c35d0114447fb50</t>
+          <t>https://www.indeed.com/viewjob?jk=0f42e6032e2d13cb</t>
         </is>
       </c>
     </row>
@@ -1763,25 +1763,25 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer, Solution Test-IQ Platform</t>
+          <t>Automation QA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51b37e2194c538e3</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ffd4fd4d17a66c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Software Engineer, Solution Test-IQ Platform</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NextPower</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1000f4bc65203865</t>
+          <t>https://www.indeed.com/viewjob?jk=51b37e2194c538e3</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Forward Deployed AI/ML Engineer IV</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b7247de0da89be</t>
+          <t>https://www.indeed.com/viewjob?jk=191a5d619c9740cd</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Scala, Kafka, Oracle, Cassandra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d42517f4a6ea31f</t>
+          <t>https://www.indeed.com/viewjob?jk=73c5cdad23779985</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae6deb5151a171c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c4c2403873b5face</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c9b376252505568</t>
+          <t>https://www.indeed.com/viewjob?jk=70157732c8210316</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283361b16a1ebc55</t>
+          <t>https://www.indeed.com/viewjob?jk=d8c55ab8d1ce73d1</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cbd383a79d4cbef</t>
+          <t>https://www.indeed.com/viewjob?jk=79b7247de0da89be</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f223b258887bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=2d42517f4a6ea31f</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4930899ea4c30eec</t>
+          <t>https://www.indeed.com/viewjob?jk=3573213c6763fded</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a609ef484a70728b</t>
+          <t>https://www.indeed.com/viewjob?jk=ae6deb5151a171c2</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d315fdda0e904f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=6c9b376252505568</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63df87d110e211fc</t>
+          <t>https://www.indeed.com/viewjob?jk=283361b16a1ebc55</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0e3854fb6006e0</t>
+          <t>https://www.indeed.com/viewjob?jk=5cbd383a79d4cbef</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=269532a3a9e4d5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=80f223b258887bd4</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dd9ebe802598879</t>
+          <t>https://www.indeed.com/viewjob?jk=4930899ea4c30eec</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e3579b3828b4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=82199ed24d8bff3e</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1cce3fa4d089a8</t>
+          <t>https://www.indeed.com/viewjob?jk=a609ef484a70728b</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdfa4a99cf1b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=d315fdda0e904f4c</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3cd1e1f07261faf</t>
+          <t>https://www.indeed.com/viewjob?jk=63df87d110e211fc</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de2979f66f2e58c</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0e3854fb6006e0</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc4c1c460908c45</t>
+          <t>https://www.indeed.com/viewjob?jk=269532a3a9e4d5a7</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a881072cca7866f9</t>
+          <t>https://www.indeed.com/viewjob?jk=5dd9ebe802598879</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bc0d51ec16f366</t>
+          <t>https://www.indeed.com/viewjob?jk=54e3579b3828b4cb</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8840753fb3651a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1cce3fa4d089a8</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f63908830628ad26</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdfa4a99cf1b0e</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a06bbcb4a7c85812</t>
+          <t>https://www.indeed.com/viewjob?jk=a3cd1e1f07261faf</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e1a7faad10c09b</t>
+          <t>https://www.indeed.com/viewjob?jk=2de2979f66f2e58c</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5df440725468089</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc4c1c460908c45</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72ebc749f6a1d990</t>
+          <t>https://www.indeed.com/viewjob?jk=a881072cca7866f9</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b631015d13883564</t>
+          <t>https://www.indeed.com/viewjob?jk=13bc0d51ec16f366</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18dc70138cc32ac9</t>
+          <t>https://www.indeed.com/viewjob?jk=8840753fb3651a4b</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85824dce6929812</t>
+          <t>https://www.indeed.com/viewjob?jk=f63908830628ad26</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd89770faca6190f</t>
+          <t>https://www.indeed.com/viewjob?jk=a06bbcb4a7c85812</t>
         </is>
       </c>
     </row>
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9109da232a7f8d</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e1a7faad10c09b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Forward Deployed AI/ML Engineer IV</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191a5d619c9740cd</t>
+          <t>https://www.indeed.com/viewjob?jk=a5df440725468089</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Scala, Kafka, Oracle, Cassandra</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73c5cdad23779985</t>
+          <t>https://www.indeed.com/viewjob?jk=72ebc749f6a1d990</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70157732c8210316</t>
+          <t>https://www.indeed.com/viewjob?jk=b631015d13883564</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c2403873b5face</t>
+          <t>https://www.indeed.com/viewjob?jk=18dc70138cc32ac9</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,102 +3296,102 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c55ab8d1ce73d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f6820c1cf060fe46</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Palantir Data Engineer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=846bf8f81216a75d</t>
+          <t>https://www.indeed.com/viewjob?jk=f85824dce6929812</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer-2</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbfd73d28e687c7</t>
+          <t>https://www.indeed.com/viewjob?jk=dd89770faca6190f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0409e471c2849f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9109da232a7f8d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior AWS Connect Engineer</t>
+          <t>Palantir Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace77f8600c9c3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=846bf8f81216a75d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior AWS Connect Engineer</t>
+          <t>Data Engineer-2</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37fb83e9052e8c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=adbfd73d28e687c7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cloud Engineer- Data/AI Focused</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Innovative Solutions</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Scala, DynamoDB</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e08a12c76721e4</t>
+          <t>https://www.indeed.com/viewjob?jk=0409e471c2849f2d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Full Stack Developer</t>
+          <t>Senior AWS Connect Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Innovative Solutions</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06271d579eb6e429</t>
+          <t>https://www.indeed.com/viewjob?jk=ace77f8600c9c3a1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Senior AWS Connect Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,19 +3576,19 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=642652601718b1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=37fb83e9052e8c4f</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Cloud Engineer- Data/AI Focused</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Innovative Solutions</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788fc3c0ac9b4619</t>
+          <t>https://www.indeed.com/viewjob?jk=33e08a12c76721e4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Cloud Engineer - Full Stack Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Osmose Utilities Services, Inc.</t>
+          <t>Innovative Solutions</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8aab16d2434e23f</t>
+          <t>https://www.indeed.com/viewjob?jk=06271d579eb6e429</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Stardog Admin/DevOps Consultant</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Astre Consulting Service Inc</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Cloud Storage, Scala, SQL Server, PostgreSQL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c930e89c4c66160</t>
+          <t>https://www.indeed.com/viewjob?jk=8a91e2ec93b2c129</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Development Engineer (DevOps)</t>
+          <t>2027 Capital Markets, Quantitative Technology Services Summer Analyst</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da39e3bd2b6b4205</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb88e40dcb32f72</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Development Engineer (DevOps)</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f7d8bd9f99d822</t>
+          <t>https://www.indeed.com/viewjob?jk=788fc3c0ac9b4619</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Development Engineer (DevOps)</t>
+          <t>Cloud-Native Architect</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a39b292b018429b6</t>
+          <t>https://www.indeed.com/viewjob?jk=642652601718b1c2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Development Engineer (DevOps)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Osmose Utilities Services, Inc.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Snowflake, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300b116043f34bac</t>
+          <t>https://www.indeed.com/viewjob?jk=b8aab16d2434e23f</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Development Engineer (DevOps)</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Astre Consulting Service Inc</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be09b22adcb2fddf</t>
+          <t>https://www.indeed.com/viewjob?jk=8c930e89c4c66160</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Development Engineer (DevOps)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, SQS, ECS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, ELT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cdf9d93c0ba359f</t>
+          <t>https://www.indeed.com/viewjob?jk=07af4f620d0cc3ad</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Development Engineer (DevOps)</t>
+          <t>Software Engineer II- Eng</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=666a4782fca49a28</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1fc3f1de5d21dc</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Quest Analytics Internship Program - Summer 2027 in Kansas City</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Quest Analytics</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, ELT</t>
+          <t>Databricks, Spark, SQL Server, MongoDB, NoSQL, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07af4f620d0cc3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=fa096b5f07acc65b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb102790d16f532</t>
+          <t>https://www.indeed.com/viewjob?jk=e06d6e56ef7c81de</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - Dallas, TX</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>SquareTrade</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2090e6291d9af573</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0a62a40f8906c0</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Optisources LLC</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,67 +4066,67 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=674588f252c63a1f</t>
+          <t>https://www.indeed.com/viewjob?jk=bd21fd4293097f4d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer II- Eng</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>Google Cloud Platform, Hadoop, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1fc3f1de5d21dc</t>
+          <t>https://www.indeed.com/viewjob?jk=11f86cdd4c675439</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Quest Analytics Internship Program - Summer 2027 in Kansas City</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Quest Analytics</t>
+          <t>EarnIn</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Databricks, Spark, SQL Server, MongoDB, NoSQL, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, Lambda, RDS, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa096b5f07acc65b</t>
+          <t>https://www.indeed.com/viewjob?jk=80f20f480a6626da</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
+          <t>AWS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06d6e56ef7c81de</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7802e0b1c362ab</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer – Enterprise Applications</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SquareTrade</t>
+          <t>Allen Control Systems</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0a62a40f8906c0</t>
+          <t>https://www.indeed.com/viewjob?jk=eaff489ad3919834</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Hadoop, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11f86cdd4c675439</t>
+          <t>https://www.indeed.com/viewjob?jk=b320160e6257e21f</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EarnIn</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, ECS, RDS, Scala, MongoDB, Data Modeling, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f20f480a6626da</t>
+          <t>https://www.indeed.com/viewjob?jk=d430b11f1930cc7f</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Architects</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>True Manufacturing</t>
+          <t>Merck KGaA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,42 +4301,42 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, IAM, RDS, Spark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>Spark, Scala, Oracle, SQL Server, PostgreSQL, Cassandra, NoSQL, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9d0346fc9e191d8</t>
+          <t>https://www.indeed.com/viewjob?jk=58202f48c352ef63</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer – Enterprise Applications</t>
+          <t>Software Engineer III - Enterprise Intelligence</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Allen Control Systems</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaff489ad3919834</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3f3c53f35b1893</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI &amp; Data Scientist Intern</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b320160e6257e21f</t>
+          <t>https://www.indeed.com/viewjob?jk=7e1b18d9ff34a767</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (hybrid)</t>
+          <t>AI &amp; Data Scientist Intern</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>York, PA, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,67 +4416,67 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c9672421189d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=222cf2907d848f0c</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core Services</t>
+          <t>Data Engineer, AI Enablement</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ellipsis Health</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb104c65d5c051e4</t>
+          <t>https://www.indeed.com/viewjob?jk=59419b9909aa5e8c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Associate Architects</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Merck KGaA</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Spark, Scala, Oracle, SQL Server, PostgreSQL, Cassandra, NoSQL, CI/CD, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58202f48c352ef63</t>
+          <t>https://www.indeed.com/viewjob?jk=991793b1299304ff</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist Intern</t>
+          <t>Applied Machine Learning Scientist II (AI/ML - Model Validation, GenAI &amp; Agentic AI)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Westchester, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e1b18d9ff34a767</t>
+          <t>https://www.indeed.com/viewjob?jk=18a45300b5503869</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist Intern</t>
+          <t>Technology Development Program Associate - August 2027</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Westchester, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222cf2907d848f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=718fa3c3e4a98b95</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Engineer, AI Enablement</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Encore Global</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Schiller Park, IL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59419b9909aa5e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=da71cda8fc390157</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991793b1299304ff</t>
+          <t>https://www.indeed.com/viewjob?jk=ba07136a4a72ee21</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Scientist II (AI/ML - Model Validation, GenAI &amp; Agentic AI)</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, Git</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a45300b5503869</t>
+          <t>https://www.indeed.com/viewjob?jk=b50e5db3bf7a0090</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Technology Development Program Associate - August 2027</t>
+          <t>Enterprise AI Systems Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
+          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=718fa3c3e4a98b95</t>
+          <t>https://www.indeed.com/viewjob?jk=90542e98749e2837</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Enterprise AI Systems Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Encore Global</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Schiller Park, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da71cda8fc390157</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba67ab5bc7e4a04</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Enterprise AI Systems Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba07136a4a72ee21</t>
+          <t>https://www.indeed.com/viewjob?jk=fe935e70dd3f2e18</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Enterprise AI Systems Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50e5db3bf7a0090</t>
+          <t>https://www.indeed.com/viewjob?jk=037741e66967443c</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Enterprise AI Systems Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90542e98749e2837</t>
+          <t>https://www.indeed.com/viewjob?jk=448bed8907ce0072</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Enterprise AI Systems Engineer</t>
+          <t>Gen AI Engineer-2</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba67ab5bc7e4a04</t>
+          <t>https://www.indeed.com/viewjob?jk=8e696b1edc4cf08e</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Enterprise AI Systems Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe935e70dd3f2e18</t>
+          <t>https://www.indeed.com/viewjob?jk=af8c2d05083f261a</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Enterprise AI Systems Engineer</t>
+          <t>Senior Software Engineer – Manufacturing Digital Operations</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, Data Modeling, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037741e66967443c</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c17d5756834ac8</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Sr Engineer - MLOps Platform(Remote Or Hybrid)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448bed8907ce0072</t>
+          <t>https://www.indeed.com/viewjob?jk=4815f622b7e398e4</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sr Engineer - MLOps Platform(Remote Or Hybrid)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Kafka, NoSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4815f622b7e398e4</t>
+          <t>https://www.indeed.com/viewjob?jk=ad396daca54f6bd7</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior LLMOps Engineer, Development</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8c2d05083f261a</t>
+          <t>https://www.indeed.com/viewjob?jk=1698a3db62a44dc8</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Gen AI Engineer-2</t>
+          <t>BI Report Developer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
+          <t>AWS, Redshift, S3, RDS, Azure, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e696b1edc4cf08e</t>
+          <t>https://www.indeed.com/viewjob?jk=b493a51345446a14</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>IT Architect - Cloud Platform</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, NoSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad396daca54f6bd7</t>
+          <t>https://www.indeed.com/viewjob?jk=e51855e99ddfa3fa</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BI Report Developer</t>
+          <t>Qualys Integration Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>UltraViolet Cyber</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, ELT, REST API integration, Splunk, Python</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5150,76 +5150,6 @@
         </is>
       </c>
       <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b493a51345446a14</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>IT Architect - Cloud Platform</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Maximus</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Tysons, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e51855e99ddfa3fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Qualys Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>UltraViolet Cyber</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, ELT, REST API integration, Splunk, Python</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1967e3fb659eb2d3</t>
         </is>

--- a/results/job_matches_2026-09-16.xlsx
+++ b/results/job_matches_2026-09-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,35 +643,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III (Full Stack)</t>
+          <t>Software Engineer II: Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sprouts Farmers Market</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Kafka, SQL Server</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9717265e88692311</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b2c0563ecfc04e</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IT Site Reliability Engineer II - Data Platforms - Remote</t>
+          <t>Senior Data Streaming Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UNFI</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8613083ecb455e28</t>
+          <t>https://www.indeed.com/viewjob?jk=f9b47adc9fda6292</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>IT Site Reliability Engineer II - Data Platforms - Remote</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>UNFI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7223f033607ba4e</t>
+          <t>https://www.indeed.com/viewjob?jk=8613083ecb455e28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer II</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Elsevier</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c4fe230bc9da32</t>
+          <t>https://www.indeed.com/viewjob?jk=a7223f033607ba4e</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Elsevier</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a3565a4a0f6c00</t>
+          <t>https://www.indeed.com/viewjob?jk=93c4fe230bc9da32</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Systems Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56823350b0e43e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a3565a4a0f6c00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dev Engineer SOW # EG CO1 B2 US</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d53cf9d0bf68048b</t>
+          <t>https://www.indeed.com/viewjob?jk=56823350b0e43e7b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Dev Engineer SOW # EG CO1 B2 US</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Concord USA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=962688fb52f665fe</t>
+          <t>https://www.indeed.com/viewjob?jk=d53cf9d0bf68048b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Medical Automation SaaS platform ( Python + data pipelines + automation</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Relentless Talent</t>
+          <t>Concord USA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3242e705b806ab21</t>
+          <t>https://www.indeed.com/viewjob?jk=962688fb52f665fe</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Software Engineer ( Gen AI)</t>
+          <t>Sr Software Engineer - Medical Automation SaaS platform ( Python + data pipelines + automation</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Blue Yonder</t>
+          <t>Relentless Talent</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a55a27bf3bdffde</t>
+          <t>https://www.indeed.com/viewjob?jk=3242e705b806ab21</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Sr Software Engineer ( Gen AI)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Blue Yonder</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772f1be866124af1</t>
+          <t>https://www.indeed.com/viewjob?jk=9a55a27bf3bdffde</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fb54968897c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=772f1be866124af1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Engineer I, DevOps</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CareMetx, LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b79178087231c2</t>
+          <t>https://www.indeed.com/viewjob?jk=52fb54968897c95b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Analyst, Production Support</t>
+          <t>Senior Engineer I, DevOps</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Expion health</t>
+          <t>CareMetx, LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Snowflake, Time Travel, MySQL, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249f623fa05a779f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b79178087231c2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Analyst, Production Support</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Expion health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Snowflake, Time Travel, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463e1932681d1ea9</t>
+          <t>https://www.indeed.com/viewjob?jk=249f623fa05a779f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0520916947bccd63</t>
+          <t>https://www.indeed.com/viewjob?jk=463e1932681d1ea9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - GCP</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Veson Nautical</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c626e90462e462c</t>
+          <t>https://www.indeed.com/viewjob?jk=0520916947bccd63</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Site Reliability Engineer - GCP</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>isolved</t>
+          <t>Veson Nautical</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b45e4d16b1cb423</t>
+          <t>https://www.indeed.com/viewjob?jk=9c626e90462e462c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mike Albert Leasing, Inc</t>
+          <t>isolved</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ad3074a940aca6</t>
+          <t>https://www.indeed.com/viewjob?jk=8b45e4d16b1cb423</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Mike Albert Leasing, Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca57e502d5a7eb</t>
+          <t>https://www.indeed.com/viewjob?jk=28ad3074a940aca6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026016 - Software Engineer II (CA)</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Moline, IL, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f2f62beea8bb80a</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca57e502d5a7eb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Trading Analytics Developer, Quantitative Trading</t>
+          <t>2026016 - Software Engineer II (CA)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CRYPTO.com</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Moline, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, MongoDB, ETL, CI/CD</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfb2225c982e0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=5f2f62beea8bb80a</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be62e17c354b320c</t>
+          <t>https://www.indeed.com/viewjob?jk=2cfb2225c982e0d3</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c35d0114447fb50</t>
+          <t>https://www.indeed.com/viewjob?jk=be62e17c354b320c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Trading Analytics Developer, Quantitative Trading</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aeroflow Health</t>
+          <t>CRYPTO.com</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f42e6032e2d13cb</t>
+          <t>https://www.indeed.com/viewjob?jk=5c35d0114447fb50</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kubernetes Platform &amp; DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Aeroflow Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morgantown, WV, US USA</t>
+          <t>Asheville, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Kafka, PostgreSQL, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Athena, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82adbdad85a792ab</t>
+          <t>https://www.indeed.com/viewjob?jk=0f42e6032e2d13cb</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b48caf12e9a2d919</t>
+          <t>https://www.indeed.com/viewjob?jk=b83169a97751389a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Kubernetes Platform &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Moderna</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Morgantown, WV, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, ELT, MLflow</t>
+          <t>AWS, S3, Azure, GCP, Kafka, PostgreSQL, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1fd9de87775b12</t>
+          <t>https://www.indeed.com/viewjob?jk=82adbdad85a792ab</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior AWS Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Random Bit</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Jenkins, Docker</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7527773abc54ea75</t>
+          <t>https://www.indeed.com/viewjob?jk=b48caf12e9a2d919</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Automation QA</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Moderna</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ffd4fd4d17a66c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d1fd9de87775b12</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer, Solution Test-IQ Platform</t>
+          <t>Senior AWS Solution Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Random Bit</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51b37e2194c538e3</t>
+          <t>https://www.indeed.com/viewjob?jk=7527773abc54ea75</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Azure Cloud Data Engineer(Korean Bilingual)</t>
+          <t>Automation QA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82fc88c444cdb59a</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ffd4fd4d17a66c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MS Fabric Data Engineer</t>
+          <t>Software Engineer, Solution Test-IQ Platform</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ovation Healthcare</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Welcome, SC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9cfdf9043d0f23</t>
+          <t>https://www.indeed.com/viewjob?jk=51b37e2194c538e3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Databricks Data Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4722e19a4c6bc57</t>
+          <t>https://www.indeed.com/viewjob?jk=c06a4bf8bf5eacf5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Cloud Data Engineer(Korean Bilingual)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JELLYFISH</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, Scala, Snowflake, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37ccdf3a9f7e654a</t>
+          <t>https://www.indeed.com/viewjob?jk=82fc88c444cdb59a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Forward Deployed AI/ML Engineer IV</t>
+          <t>MS Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Ovation Healthcare</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Welcome, SC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191a5d619c9740cd</t>
+          <t>https://www.indeed.com/viewjob?jk=fa9cfdf9043d0f23</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer</t>
+          <t>Sr. Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Scala, Kafka, Oracle, Cassandra</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73c5cdad23779985</t>
+          <t>https://www.indeed.com/viewjob?jk=d4722e19a4c6bc57</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>JELLYFISH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c2403873b5face</t>
+          <t>https://www.indeed.com/viewjob?jk=37ccdf3a9f7e654a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Sr Full Stack Engineer, Platform Services</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>College Board</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70157732c8210316</t>
+          <t>https://www.indeed.com/viewjob?jk=b325145434e13d25</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Forward Deployed AI/ML Engineer IV</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c55ab8d1ce73d1</t>
+          <t>https://www.indeed.com/viewjob?jk=191a5d619c9740cd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Scala, Kafka, Oracle, Cassandra</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b7247de0da89be</t>
+          <t>https://www.indeed.com/viewjob?jk=73c5cdad23779985</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d42517f4a6ea31f</t>
+          <t>https://www.indeed.com/viewjob?jk=c4c2403873b5face</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3573213c6763fded</t>
+          <t>https://www.indeed.com/viewjob?jk=70157732c8210316</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae6deb5151a171c2</t>
+          <t>https://www.indeed.com/viewjob?jk=79b7247de0da89be</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c9b376252505568</t>
+          <t>https://www.indeed.com/viewjob?jk=2d42517f4a6ea31f</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283361b16a1ebc55</t>
+          <t>https://www.indeed.com/viewjob?jk=3573213c6763fded</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cbd383a79d4cbef</t>
+          <t>https://www.indeed.com/viewjob?jk=ae6deb5151a171c2</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f223b258887bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=6c9b376252505568</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4930899ea4c30eec</t>
+          <t>https://www.indeed.com/viewjob?jk=283361b16a1ebc55</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82199ed24d8bff3e</t>
+          <t>https://www.indeed.com/viewjob?jk=5cbd383a79d4cbef</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a609ef484a70728b</t>
+          <t>https://www.indeed.com/viewjob?jk=80f223b258887bd4</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d315fdda0e904f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=4930899ea4c30eec</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63df87d110e211fc</t>
+          <t>https://www.indeed.com/viewjob?jk=82199ed24d8bff3e</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0e3854fb6006e0</t>
+          <t>https://www.indeed.com/viewjob?jk=a609ef484a70728b</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=269532a3a9e4d5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=d315fdda0e904f4c</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dd9ebe802598879</t>
+          <t>https://www.indeed.com/viewjob?jk=63df87d110e211fc</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e3579b3828b4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0e3854fb6006e0</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1cce3fa4d089a8</t>
+          <t>https://www.indeed.com/viewjob?jk=269532a3a9e4d5a7</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdfa4a99cf1b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=5dd9ebe802598879</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3cd1e1f07261faf</t>
+          <t>https://www.indeed.com/viewjob?jk=54e3579b3828b4cb</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de2979f66f2e58c</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1cce3fa4d089a8</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc4c1c460908c45</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdfa4a99cf1b0e</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a881072cca7866f9</t>
+          <t>https://www.indeed.com/viewjob?jk=a3cd1e1f07261faf</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bc0d51ec16f366</t>
+          <t>https://www.indeed.com/viewjob?jk=2de2979f66f2e58c</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8840753fb3651a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc4c1c460908c45</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f63908830628ad26</t>
+          <t>https://www.indeed.com/viewjob?jk=a881072cca7866f9</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a06bbcb4a7c85812</t>
+          <t>https://www.indeed.com/viewjob?jk=13bc0d51ec16f366</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e1a7faad10c09b</t>
+          <t>https://www.indeed.com/viewjob?jk=8840753fb3651a4b</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5df440725468089</t>
+          <t>https://www.indeed.com/viewjob?jk=f63908830628ad26</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72ebc749f6a1d990</t>
+          <t>https://www.indeed.com/viewjob?jk=a06bbcb4a7c85812</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b631015d13883564</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e1a7faad10c09b</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18dc70138cc32ac9</t>
+          <t>https://www.indeed.com/viewjob?jk=a5df440725468089</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6820c1cf060fe46</t>
+          <t>https://www.indeed.com/viewjob?jk=72ebc749f6a1d990</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85824dce6929812</t>
+          <t>https://www.indeed.com/viewjob?jk=b631015d13883564</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd89770faca6190f</t>
+          <t>https://www.indeed.com/viewjob?jk=18dc70138cc32ac9</t>
         </is>
       </c>
     </row>
@@ -3401,102 +3401,102 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9109da232a7f8d</t>
+          <t>https://www.indeed.com/viewjob?jk=f6820c1cf060fe46</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Palantir Data Engineer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=846bf8f81216a75d</t>
+          <t>https://www.indeed.com/viewjob?jk=f85824dce6929812</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer-2</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbfd73d28e687c7</t>
+          <t>https://www.indeed.com/viewjob?jk=dd89770faca6190f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0409e471c2849f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9109da232a7f8d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior AWS Connect Engineer</t>
+          <t>Data Engineer-2</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace77f8600c9c3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=adbfd73d28e687c7</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior AWS Connect Engineer</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37fb83e9052e8c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=0409e471c2849f2d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cloud Engineer- Data/AI Focused</t>
+          <t>Senior AWS Connect Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Innovative Solutions</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e08a12c76721e4</t>
+          <t>https://www.indeed.com/viewjob?jk=ace77f8600c9c3a1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Full Stack Developer</t>
+          <t>Senior AWS Connect Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Innovative Solutions</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06271d579eb6e429</t>
+          <t>https://www.indeed.com/viewjob?jk=37fb83e9052e8c4f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Stardog Admin/DevOps Consultant</t>
+          <t>Cloud Engineer- Data/AI Focused</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Innovative Solutions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Cloud Storage, Scala, SQL Server, PostgreSQL, ELT, CI/CD, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a91e2ec93b2c129</t>
+          <t>https://www.indeed.com/viewjob?jk=33e08a12c76721e4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2027 Capital Markets, Quantitative Technology Services Summer Analyst</t>
+          <t>Cloud Engineer - Full Stack Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>Innovative Solutions</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb88e40dcb32f72</t>
+          <t>https://www.indeed.com/viewjob?jk=06271d579eb6e429</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Stardog Admin/DevOps Consultant</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Cloud Storage, Scala, SQL Server, PostgreSQL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788fc3c0ac9b4619</t>
+          <t>https://www.indeed.com/viewjob?jk=8a91e2ec93b2c129</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>2027 Capital Markets, Quantitative Technology Services Summer Analyst</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=642652601718b1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb88e40dcb32f72</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Osmose Utilities Services, Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8aab16d2434e23f</t>
+          <t>https://www.indeed.com/viewjob?jk=788fc3c0ac9b4619</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Cloud-Native Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Astre Consulting Service Inc</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c930e89c4c66160</t>
+          <t>https://www.indeed.com/viewjob?jk=642652601718b1c2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Osmose Utilities Services, Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, ELT</t>
+          <t>AWS, RDS, Azure, Snowflake, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07af4f620d0cc3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=b8aab16d2434e23f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer II- Eng</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>Astre Consulting Service Inc</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1fc3f1de5d21dc</t>
+          <t>https://www.indeed.com/viewjob?jk=8c930e89c4c66160</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Quest Analytics Internship Program - Summer 2027 in Kansas City</t>
+          <t>Software Engineer II- Eng</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Quest Analytics</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,42 +3951,42 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Databricks, Spark, SQL Server, MongoDB, NoSQL, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa096b5f07acc65b</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1fc3f1de5d21dc</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Quest Analytics Internship Program - Summer 2027 in Kansas City</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Quest Analytics</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
+          <t>Databricks, Spark, SQL Server, MongoDB, NoSQL, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06d6e56ef7c81de</t>
+          <t>https://www.indeed.com/viewjob?jk=fa096b5f07acc65b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SquareTrade</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0a62a40f8906c0</t>
+          <t>https://www.indeed.com/viewjob?jk=e06d6e56ef7c81de</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>SquareTrade</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd21fd4293097f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0a62a40f8906c0</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Hadoop, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11f86cdd4c675439</t>
+          <t>https://www.indeed.com/viewjob?jk=bd21fd4293097f4d</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>EarnIn</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>Google Cloud Platform, Hadoop, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f20f480a6626da</t>
+          <t>https://www.indeed.com/viewjob?jk=11f86cdd4c675439</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>EarnIn</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, RDS, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7802e0b1c362ab</t>
+          <t>https://www.indeed.com/viewjob?jk=80f20f480a6626da</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer – Enterprise Applications</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Allen Control Systems</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaff489ad3919834</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7802e0b1c362ab</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Database Administrator - PostgreSQL Carmel, United States Sep. 15, 2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Alter Domus</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b320160e6257e21f</t>
+          <t>https://www.indeed.com/viewjob?jk=466ef9cc01d7f367</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Staples</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, MongoDB, Data Modeling, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d430b11f1930cc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=d260e41a66c285a8</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Associate Architects</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Merck KGaA</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Spark, Scala, Oracle, SQL Server, PostgreSQL, Cassandra, NoSQL, CI/CD, Maven, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Kafka, SQL Server, PostgreSQL, MongoDB, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58202f48c352ef63</t>
+          <t>https://www.indeed.com/viewjob?jk=1200afb16be7a459</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer III - Enterprise Intelligence</t>
+          <t>Software Engineer – Enterprise Applications</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Allen Control Systems</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3f3c53f35b1893</t>
+          <t>https://www.indeed.com/viewjob?jk=eaff489ad3919834</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist Intern</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Westchester, IL, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e1b18d9ff34a767</t>
+          <t>https://www.indeed.com/viewjob?jk=b320160e6257e21f</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist Intern</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Westchester, IL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, ECS, RDS, Scala, MongoDB, Data Modeling, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222cf2907d848f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=d430b11f1930cc7f</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer, AI Enablement</t>
+          <t>Associate Architects</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Merck KGaA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>Spark, Scala, Oracle, SQL Server, PostgreSQL, Cassandra, NoSQL, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59419b9909aa5e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=58202f48c352ef63</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer III - Enterprise Intelligence</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991793b1299304ff</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3f3c53f35b1893</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Scientist II (AI/ML - Model Validation, GenAI &amp; Agentic AI)</t>
+          <t>AI &amp; Data Scientist Intern</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a45300b5503869</t>
+          <t>https://www.indeed.com/viewjob?jk=7e1b18d9ff34a767</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Technology Development Program Associate - August 2027</t>
+          <t>AI &amp; Data Scientist Intern</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=718fa3c3e4a98b95</t>
+          <t>https://www.indeed.com/viewjob?jk=222cf2907d848f0c</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Data Engineer, AI Enablement</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Encore Global</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Schiller Park, IL, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da71cda8fc390157</t>
+          <t>https://www.indeed.com/viewjob?jk=59419b9909aa5e8c</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba07136a4a72ee21</t>
+          <t>https://www.indeed.com/viewjob?jk=991793b1299304ff</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Applied Machine Learning Scientist II (AI/ML - Model Validation, GenAI &amp; Agentic AI)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50e5db3bf7a0090</t>
+          <t>https://www.indeed.com/viewjob?jk=18a45300b5503869</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Enterprise AI Systems Engineer</t>
+          <t>Technology Development Program Associate - August 2027</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
+          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90542e98749e2837</t>
+          <t>https://www.indeed.com/viewjob?jk=718fa3c3e4a98b95</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Enterprise AI Systems Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Encore Global</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Schiller Park, IL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba67ab5bc7e4a04</t>
+          <t>https://www.indeed.com/viewjob?jk=da71cda8fc390157</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Enterprise AI Systems Engineer</t>
+          <t>Senior TDI Site Reliability Engineer, Okta Federal</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe935e70dd3f2e18</t>
+          <t>https://www.indeed.com/viewjob?jk=180e2e1d120eeb3a</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Enterprise AI Systems Engineer</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037741e66967443c</t>
+          <t>https://www.indeed.com/viewjob?jk=b50e5db3bf7a0090</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Enterprise AI Systems Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448bed8907ce0072</t>
+          <t>https://www.indeed.com/viewjob?jk=90542e98749e2837</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Gen AI Engineer-2</t>
+          <t>Enterprise AI Systems Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
+          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e696b1edc4cf08e</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba67ab5bc7e4a04</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Enterprise AI Systems Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8c2d05083f261a</t>
+          <t>https://www.indeed.com/viewjob?jk=fe935e70dd3f2e18</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Manufacturing Digital Operations</t>
+          <t>Enterprise AI Systems Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, Data Modeling, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c17d5756834ac8</t>
+          <t>https://www.indeed.com/viewjob?jk=037741e66967443c</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sr Engineer - MLOps Platform(Remote Or Hybrid)</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4815f622b7e398e4</t>
+          <t>https://www.indeed.com/viewjob?jk=448bed8907ce0072</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Gen AI Engineer-2</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, NoSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad396daca54f6bd7</t>
+          <t>https://www.indeed.com/viewjob?jk=8e696b1edc4cf08e</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior LLMOps Engineer, Development</t>
+          <t>Senior Software Engineer – Manufacturing Digital Operations</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, Data Modeling, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1698a3db62a44dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c17d5756834ac8</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BI Report Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, NoSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b493a51345446a14</t>
+          <t>https://www.indeed.com/viewjob?jk=ad396daca54f6bd7</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>IT Architect - Cloud Platform</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e51855e99ddfa3fa</t>
+          <t>https://www.indeed.com/viewjob?jk=af8c2d05083f261a</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Qualys Integration Engineer</t>
+          <t>Senior LLMOps Engineer, Development</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>UltraViolet Cyber</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,15 +5141,120 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1698a3db62a44dc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>BI Report Developer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Topgolf</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, RDS, Azure, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b493a51345446a14</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Sr Engineer - MLOps Platform(Remote Or Hybrid)</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Brooklyn Park, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4815f622b7e398e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Qualys Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>UltraViolet Cyber</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, ELT, REST API integration, Splunk, Python</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1967e3fb659eb2d3</t>
         </is>

--- a/results/job_matches_2026-09-16.xlsx
+++ b/results/job_matches_2026-09-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>AWS Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vdrive IT Solutions, Inc</t>
+          <t>Trianz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Clinton, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27.8</v>
+        <v>21.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Data Lake Storage</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,94 +566,94 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667cfa1dd76c2ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=60852d74dc99179b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AWS Data Architect</t>
+          <t>Sr. AI/Python Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Trianz</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Clinton, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, ECS, RDS, Vertex AI, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60852d74dc99179b</t>
+          <t>https://www.indeed.com/viewjob?jk=2668edd7349e606b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Software Engineer II: Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BJ's Wholesale Club</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e0754a22ac91db2</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b2c0563ecfc04e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer II: Data Engineer</t>
+          <t>Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Acxiom</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Conway, AR, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, S3, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b2c0563ecfc04e</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb6bc702cc8f819</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Intern - Data Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Acxiom</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Conway, AR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb6bc702cc8f819</t>
+          <t>https://www.indeed.com/viewjob?jk=269ed9811c4ddaf1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Go (Golang) Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BankUnited</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Miami Lakes, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, MongoDB, Cassandra</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cce5aca3307e7b11</t>
+          <t>https://www.indeed.com/viewjob?jk=1604fae578cd1b7c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Go (Golang) Developer</t>
+          <t>Senior Data Streaming Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1604fae578cd1b7c</t>
+          <t>https://www.indeed.com/viewjob?jk=f9b47adc9fda6292</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Streaming Engineer</t>
+          <t>IT Site Reliability Engineer II - Data Platforms - Remote</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>UNFI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9b47adc9fda6292</t>
+          <t>https://www.indeed.com/viewjob?jk=8613083ecb455e28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IT Site Reliability Engineer II - Data Platforms - Remote</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UNFI</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8613083ecb455e28</t>
+          <t>https://www.indeed.com/viewjob?jk=a7223f033607ba4e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Systems Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Elsevier</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7223f033607ba4e</t>
+          <t>https://www.indeed.com/viewjob?jk=93c4fe230bc9da32</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Elsevier</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c4fe230bc9da32</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a3565a4a0f6c00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a3565a4a0f6c00</t>
+          <t>https://www.indeed.com/viewjob?jk=56823350b0e43e7b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Dev Engineer SOW # EG CO1 B2 US</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56823350b0e43e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=d53cf9d0bf68048b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dev Engineer SOW # EG CO1 B2 US</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Concord USA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d53cf9d0bf68048b</t>
+          <t>https://www.indeed.com/viewjob?jk=962688fb52f665fe</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Sr Software Engineer - Medical Automation SaaS platform ( Python + data pipelines + automation</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Concord USA</t>
+          <t>Relentless Talent</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=962688fb52f665fe</t>
+          <t>https://www.indeed.com/viewjob?jk=3242e705b806ab21</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Medical Automation SaaS platform ( Python + data pipelines + automation</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Relentless Talent</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3242e705b806ab21</t>
+          <t>https://www.indeed.com/viewjob?jk=772f1be866124af1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Software Engineer ( Gen AI)</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Blue Yonder</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a55a27bf3bdffde</t>
+          <t>https://www.indeed.com/viewjob?jk=52fb54968897c95b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Senior Engineer I, DevOps</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CareMetx, LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772f1be866124af1</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b79178087231c2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>Analyst, Production Support</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Expion health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Snowflake, Time Travel, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fb54968897c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=249f623fa05a779f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Engineer I, DevOps</t>
+          <t>Data Solutions Engineer - Hybrid / Durham, NC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CareMetx, LLC</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b79178087231c2</t>
+          <t>https://www.indeed.com/viewjob?jk=186bcafa22d4b760</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Analyst, Production Support</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Expion health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Snowflake, Time Travel, MySQL, Data Modeling</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249f623fa05a779f</t>
+          <t>https://www.indeed.com/viewjob?jk=0520916947bccd63</t>
         </is>
       </c>
     </row>
@@ -1308,35 +1308,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ebbo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0520916947bccd63</t>
+          <t>https://www.indeed.com/viewjob?jk=00129c0be2bb43b6</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>2026016 - Software Engineer II (CA)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mike Albert Leasing, Inc</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Moline, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ad3074a940aca6</t>
+          <t>https://www.indeed.com/viewjob?jk=5f2f62beea8bb80a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>Trading Analytics Developer, Quantitative Trading</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>CRYPTO.com</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca57e502d5a7eb</t>
+          <t>https://www.indeed.com/viewjob?jk=2cfb2225c982e0d3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026016 - Software Engineer II (CA)</t>
+          <t>Trading Analytics Developer, Quantitative Trading</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>CRYPTO.com</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Moline, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f2f62beea8bb80a</t>
+          <t>https://www.indeed.com/viewjob?jk=be62e17c354b320c</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfb2225c982e0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=5c35d0114447fb50</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Trading Analytics Developer, Quantitative Trading</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CRYPTO.com</t>
+          <t>Aeroflow Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Asheville, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, MongoDB, ETL, CI/CD</t>
+          <t>AWS, Glue, Athena, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be62e17c354b320c</t>
+          <t>https://www.indeed.com/viewjob?jk=0f42e6032e2d13cb</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Trading Analytics Developer, Quantitative Trading</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CRYPTO.com</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, MongoDB, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c35d0114447fb50</t>
+          <t>https://www.indeed.com/viewjob?jk=b83169a97751389a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kubernetes Platform &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aeroflow Health</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Morgantown, WV, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, Azure, GCP, Kafka, PostgreSQL, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f42e6032e2d13cb</t>
+          <t>https://www.indeed.com/viewjob?jk=82adbdad85a792ab</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83169a97751389a</t>
+          <t>https://www.indeed.com/viewjob?jk=b48caf12e9a2d919</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kubernetes Platform &amp; DevOps Engineer</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Moderna</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morgantown, WV, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Kafka, PostgreSQL, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82adbdad85a792ab</t>
+          <t>https://www.indeed.com/viewjob?jk=7d1fd9de87775b12</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Automation QA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,42 +1746,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b48caf12e9a2d919</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ffd4fd4d17a66c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Software Engineer, Solution Test-IQ Platform</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Moderna</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, ELT, MLflow</t>
+          <t>AWS, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1fd9de87775b12</t>
+          <t>https://www.indeed.com/viewjob?jk=51b37e2194c538e3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior AWS Solution Architect</t>
+          <t>Data Platform Engineer (Associate)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Random Bit</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Jenkins, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7527773abc54ea75</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7fc7e8196397da</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Automation QA</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ffd4fd4d17a66c</t>
+          <t>https://www.indeed.com/viewjob?jk=c06a4bf8bf5eacf5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer, Solution Test-IQ Platform</t>
+          <t>Azure Cloud Data Engineer(Korean Bilingual)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51b37e2194c538e3</t>
+          <t>https://www.indeed.com/viewjob?jk=82fc88c444cdb59a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>MS Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Ovation Healthcare</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Welcome, SC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06a4bf8bf5eacf5</t>
+          <t>https://www.indeed.com/viewjob?jk=fa9cfdf9043d0f23</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Azure Cloud Data Engineer(Korean Bilingual)</t>
+          <t>Sr. Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82fc88c444cdb59a</t>
+          <t>https://www.indeed.com/viewjob?jk=d4722e19a4c6bc57</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MS Fabric Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ovation Healthcare</t>
+          <t>JELLYFISH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Welcome, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9cfdf9043d0f23</t>
+          <t>https://www.indeed.com/viewjob?jk=37ccdf3a9f7e654a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Databricks Data Engineer</t>
+          <t>Sr Full Stack Engineer, Platform Services</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>College Board</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,29 +2026,29 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4722e19a4c6bc57</t>
+          <t>https://www.indeed.com/viewjob?jk=b325145434e13d25</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Forward Deployed AI/ML Engineer IV</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JELLYFISH</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37ccdf3a9f7e654a</t>
+          <t>https://www.indeed.com/viewjob?jk=191a5d619c9740cd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Full Stack Engineer, Platform Services</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>College Board</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,29 +2096,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b325145434e13d25</t>
+          <t>https://www.indeed.com/viewjob?jk=c4c2403873b5face</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Forward Deployed AI/ML Engineer IV</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191a5d619c9740cd</t>
+          <t>https://www.indeed.com/viewjob?jk=70157732c8210316</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Scala, Kafka, Oracle, Cassandra</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73c5cdad23779985</t>
+          <t>https://www.indeed.com/viewjob?jk=79b7247de0da89be</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c2403873b5face</t>
+          <t>https://www.indeed.com/viewjob?jk=2d42517f4a6ea31f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70157732c8210316</t>
+          <t>https://www.indeed.com/viewjob?jk=3573213c6763fded</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b7247de0da89be</t>
+          <t>https://www.indeed.com/viewjob?jk=ae6deb5151a171c2</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d42517f4a6ea31f</t>
+          <t>https://www.indeed.com/viewjob?jk=6c9b376252505568</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3573213c6763fded</t>
+          <t>https://www.indeed.com/viewjob?jk=283361b16a1ebc55</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae6deb5151a171c2</t>
+          <t>https://www.indeed.com/viewjob?jk=5cbd383a79d4cbef</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c9b376252505568</t>
+          <t>https://www.indeed.com/viewjob?jk=80f223b258887bd4</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283361b16a1ebc55</t>
+          <t>https://www.indeed.com/viewjob?jk=4930899ea4c30eec</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cbd383a79d4cbef</t>
+          <t>https://www.indeed.com/viewjob?jk=82199ed24d8bff3e</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f223b258887bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=a609ef484a70728b</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4930899ea4c30eec</t>
+          <t>https://www.indeed.com/viewjob?jk=d315fdda0e904f4c</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82199ed24d8bff3e</t>
+          <t>https://www.indeed.com/viewjob?jk=63df87d110e211fc</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a609ef484a70728b</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0e3854fb6006e0</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d315fdda0e904f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=269532a3a9e4d5a7</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63df87d110e211fc</t>
+          <t>https://www.indeed.com/viewjob?jk=5dd9ebe802598879</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0e3854fb6006e0</t>
+          <t>https://www.indeed.com/viewjob?jk=54e3579b3828b4cb</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=269532a3a9e4d5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1cce3fa4d089a8</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dd9ebe802598879</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdfa4a99cf1b0e</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e3579b3828b4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=a3cd1e1f07261faf</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1cce3fa4d089a8</t>
+          <t>https://www.indeed.com/viewjob?jk=2de2979f66f2e58c</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdfa4a99cf1b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc4c1c460908c45</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3cd1e1f07261faf</t>
+          <t>https://www.indeed.com/viewjob?jk=a881072cca7866f9</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de2979f66f2e58c</t>
+          <t>https://www.indeed.com/viewjob?jk=13bc0d51ec16f366</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc4c1c460908c45</t>
+          <t>https://www.indeed.com/viewjob?jk=8840753fb3651a4b</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a881072cca7866f9</t>
+          <t>https://www.indeed.com/viewjob?jk=f63908830628ad26</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bc0d51ec16f366</t>
+          <t>https://www.indeed.com/viewjob?jk=a06bbcb4a7c85812</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8840753fb3651a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e1a7faad10c09b</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f63908830628ad26</t>
+          <t>https://www.indeed.com/viewjob?jk=a5df440725468089</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a06bbcb4a7c85812</t>
+          <t>https://www.indeed.com/viewjob?jk=72ebc749f6a1d990</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e1a7faad10c09b</t>
+          <t>https://www.indeed.com/viewjob?jk=b631015d13883564</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5df440725468089</t>
+          <t>https://www.indeed.com/viewjob?jk=18dc70138cc32ac9</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72ebc749f6a1d990</t>
+          <t>https://www.indeed.com/viewjob?jk=f6820c1cf060fe46</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b631015d13883564</t>
+          <t>https://www.indeed.com/viewjob?jk=f85824dce6929812</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18dc70138cc32ac9</t>
+          <t>https://www.indeed.com/viewjob?jk=dd89770faca6190f</t>
         </is>
       </c>
     </row>
@@ -3401,129 +3401,129 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6820c1cf060fe46</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9109da232a7f8d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Platform Engineer III</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Sinch</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, DynamoDB, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85824dce6929812</t>
+          <t>https://www.indeed.com/viewjob?jk=cc06fce927a41534</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd89770faca6190f</t>
+          <t>https://www.indeed.com/viewjob?jk=3504f95af705a178</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Data Engineer-2</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9109da232a7f8d</t>
+          <t>https://www.indeed.com/viewjob?jk=adbfd73d28e687c7</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer-2</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbfd73d28e687c7</t>
+          <t>https://www.indeed.com/viewjob?jk=0409e471c2849f2d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Senior AWS Connect Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0409e471c2849f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=ace77f8600c9c3a1</t>
         </is>
       </c>
     </row>
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace77f8600c9c3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=37fb83e9052e8c4f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior AWS Connect Engineer</t>
+          <t>Cloud Engineer- Data/AI Focused</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Innovative Solutions</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,24 +3636,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37fb83e9052e8c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=33e08a12c76721e4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cloud Engineer- Data/AI Focused</t>
+          <t>Cloud Engineer - Full Stack Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e08a12c76721e4</t>
+          <t>https://www.indeed.com/viewjob?jk=06271d579eb6e429</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Full Stack Developer</t>
+          <t>Senior Stardog Admin/DevOps Consultant</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Innovative Solutions</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Cloud Storage, Scala, SQL Server, PostgreSQL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06271d579eb6e429</t>
+          <t>https://www.indeed.com/viewjob?jk=66fe2f823196d7aa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Stardog Admin/DevOps Consultant</t>
+          <t>SQL Server DBA</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Cloud Storage, Scala, SQL Server, PostgreSQL, ELT, CI/CD, Docker</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a91e2ec93b2c129</t>
+          <t>https://www.indeed.com/viewjob?jk=2342678cabeb9fcd</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2027 Capital Markets, Quantitative Technology Services Summer Analyst</t>
+          <t>SQL Server DBA</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb88e40dcb32f72</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea93dcbac7e86e9</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>SQL Server DBA</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788fc3c0ac9b4619</t>
+          <t>https://www.indeed.com/viewjob?jk=628c74eaec435595</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Stardog Admin</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Cloud Storage, Scala, SQL Server, PostgreSQL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=642652601718b1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=13a16d396aacef30</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Stardog Admin/DevOps Consultant</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Osmose Utilities Services, Inc.</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Cloud Storage, Scala, SQL Server, PostgreSQL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8aab16d2434e23f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a91e2ec93b2c129</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>2027 Capital Markets, Quantitative Technology Services Summer Analyst</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Astre Consulting Service Inc</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c930e89c4c66160</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb88e40dcb32f72</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer II- Eng</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1fc3f1de5d21dc</t>
+          <t>https://www.indeed.com/viewjob?jk=788fc3c0ac9b4619</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Quest Analytics Internship Program - Summer 2027 in Kansas City</t>
+          <t>Software Engineer II- Eng</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Quest Analytics</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,42 +3986,42 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Databricks, Spark, SQL Server, MongoDB, NoSQL, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa096b5f07acc65b</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1fc3f1de5d21dc</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Quest Analytics Internship Program - Summer 2027 in Kansas City</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Quest Analytics</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
+          <t>Databricks, Spark, SQL Server, MongoDB, NoSQL, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,59 +4031,59 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06d6e56ef7c81de</t>
+          <t>https://www.indeed.com/viewjob?jk=fa096b5f07acc65b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SquareTrade</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, MongoDB, Azure Cosmos DB, NoSQL, ETL, Azure DevOps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0a62a40f8906c0</t>
+          <t>https://www.indeed.com/viewjob?jk=45ee9b464c973901</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd21fd4293097f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=e06d6e56ef7c81de</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>SquareTrade</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Hadoop, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11f86cdd4c675439</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0a62a40f8906c0</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>EarnIn</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f20f480a6626da</t>
+          <t>https://www.indeed.com/viewjob?jk=6629a97b773e9046</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7802e0b1c362ab</t>
+          <t>https://www.indeed.com/viewjob?jk=bd21fd4293097f4d</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Database Administrator - PostgreSQL Carmel, United States Sep. 15, 2026</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Alter Domus</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>Google Cloud Platform, Hadoop, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=466ef9cc01d7f367</t>
+          <t>https://www.indeed.com/viewjob?jk=11f86cdd4c675439</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>EarnIn</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, MLOps, Git, Python</t>
+          <t>AWS, Lambda, RDS, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d260e41a66c285a8</t>
+          <t>https://www.indeed.com/viewjob?jk=80f20f480a6626da</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Kafka, SQL Server, PostgreSQL, MongoDB, Cassandra, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1200afb16be7a459</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7802e0b1c362ab</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer – Enterprise Applications</t>
+          <t>Senior Database Administrator - PostgreSQL Carmel, United States Sep. 15, 2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Allen Control Systems</t>
+          <t>Alter Domus</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaff489ad3919834</t>
+          <t>https://www.indeed.com/viewjob?jk=466ef9cc01d7f367</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Kafka, SQL Server, PostgreSQL, MongoDB, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b320160e6257e21f</t>
+          <t>https://www.indeed.com/viewjob?jk=1200afb16be7a459</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer – Enterprise Applications</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Allen Control Systems</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, MongoDB, Data Modeling, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d430b11f1930cc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=eaff489ad3919834</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Associate Architects</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Merck KGaA</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Spark, Scala, Oracle, SQL Server, PostgreSQL, Cassandra, NoSQL, CI/CD, Maven, Terraform</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58202f48c352ef63</t>
+          <t>https://www.indeed.com/viewjob?jk=b320160e6257e21f</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineer III - Enterprise Intelligence</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Scala, MongoDB, Data Modeling, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3f3c53f35b1893</t>
+          <t>https://www.indeed.com/viewjob?jk=d430b11f1930cc7f</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist Intern</t>
+          <t>Associate Architects</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>Merck KGaA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Westchester, IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>Spark, Scala, Oracle, SQL Server, PostgreSQL, Cassandra, NoSQL, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e1b18d9ff34a767</t>
+          <t>https://www.indeed.com/viewjob?jk=58202f48c352ef63</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Westchester, IL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, Snowflake, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222cf2907d848f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=39e8077574f9d2d1</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Engineer, AI Enablement</t>
+          <t>Software Engineer III - Enterprise Intelligence</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59419b9909aa5e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3f3c53f35b1893</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AI &amp; Data Scientist Intern</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991793b1299304ff</t>
+          <t>https://www.indeed.com/viewjob?jk=7e1b18d9ff34a767</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Scientist II (AI/ML - Model Validation, GenAI &amp; Agentic AI)</t>
+          <t>AI &amp; Data Scientist Intern</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a45300b5503869</t>
+          <t>https://www.indeed.com/viewjob?jk=222cf2907d848f0c</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Technology Development Program Associate - August 2027</t>
+          <t>Data Engineer, AI Enablement</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=718fa3c3e4a98b95</t>
+          <t>https://www.indeed.com/viewjob?jk=59419b9909aa5e8c</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Encore Global</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Schiller Park, IL, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da71cda8fc390157</t>
+          <t>https://www.indeed.com/viewjob?jk=991793b1299304ff</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior TDI Site Reliability Engineer, Okta Federal</t>
+          <t>Technology Development Program Associate - August 2027</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180e2e1d120eeb3a</t>
+          <t>https://www.indeed.com/viewjob?jk=718fa3c3e4a98b95</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Encore Global</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Schiller Park, IL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50e5db3bf7a0090</t>
+          <t>https://www.indeed.com/viewjob?jk=da71cda8fc390157</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Enterprise AI Systems Engineer</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90542e98749e2837</t>
+          <t>https://www.indeed.com/viewjob?jk=b50e5db3bf7a0090</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba67ab5bc7e4a04</t>
+          <t>https://www.indeed.com/viewjob?jk=90542e98749e2837</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe935e70dd3f2e18</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba67ab5bc7e4a04</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037741e66967443c</t>
+          <t>https://www.indeed.com/viewjob?jk=fe935e70dd3f2e18</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Enterprise AI Systems Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448bed8907ce0072</t>
+          <t>https://www.indeed.com/viewjob?jk=037741e66967443c</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Gen AI Engineer-2</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e696b1edc4cf08e</t>
+          <t>https://www.indeed.com/viewjob?jk=448bed8907ce0072</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Manufacturing Digital Operations</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, Data Modeling, Azure DevOps, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c17d5756834ac8</t>
+          <t>https://www.indeed.com/viewjob?jk=af8c2d05083f261a</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer – Manufacturing Digital Operations</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, NoSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, Data Modeling, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad396daca54f6bd7</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c17d5756834ac8</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior LLMOps Engineer, Development</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8c2d05083f261a</t>
+          <t>https://www.indeed.com/viewjob?jk=1698a3db62a44dc8</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior LLMOps Engineer, Development</t>
+          <t>BI Report Developer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, S3, RDS, Azure, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1698a3db62a44dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=b493a51345446a14</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BI Report Developer</t>
+          <t>Qualys Integration Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>UltraViolet Cyber</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, ELT, REST API integration, Splunk, Python</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5185,76 +5185,6 @@
         </is>
       </c>
       <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b493a51345446a14</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Sr Engineer - MLOps Platform(Remote Or Hybrid)</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Brooklyn Park, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4815f622b7e398e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Qualys Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>UltraViolet Cyber</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, ELT, REST API integration, Splunk, Python</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1967e3fb659eb2d3</t>
         </is>

--- a/results/job_matches_2026-09-16.xlsx
+++ b/results/job_matches_2026-09-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G136"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,52 +713,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Go (Golang) Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1604fae578cd1b7c</t>
+          <t>https://www.indeed.com/viewjob?jk=7b88cb40099cd54b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Streaming Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9b47adc9fda6292</t>
+          <t>https://www.indeed.com/viewjob?jk=cc8620f42415bd69</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IT Site Reliability Engineer II - Data Platforms - Remote</t>
+          <t>Senior Data Streaming Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UNFI</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8613083ecb455e28</t>
+          <t>https://www.indeed.com/viewjob?jk=f9b47adc9fda6292</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>IT Site Reliability Engineer II - Data Platforms - Remote</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>UNFI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7223f033607ba4e</t>
+          <t>https://www.indeed.com/viewjob?jk=8613083ecb455e28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer II</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Elsevier</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c4fe230bc9da32</t>
+          <t>https://www.indeed.com/viewjob?jk=a7223f033607ba4e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer II</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Concord USA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a3565a4a0f6c00</t>
+          <t>https://www.indeed.com/viewjob?jk=962688fb52f665fe</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Software Engineer - Medical Automation SaaS platform ( Python + data pipelines + automation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Relentless Talent</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56823350b0e43e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=3242e705b806ab21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dev Engineer SOW # EG CO1 B2 US</t>
+          <t>Analyst, Production Support</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Expion health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Snowflake, Time Travel, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d53cf9d0bf68048b</t>
+          <t>https://www.indeed.com/viewjob?jk=249f623fa05a779f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Concord USA</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, SQL Server</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=962688fb52f665fe</t>
+          <t>https://www.indeed.com/viewjob?jk=772f1be866124af1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Medical Automation SaaS platform ( Python + data pipelines + automation</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Relentless Talent</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3242e705b806ab21</t>
+          <t>https://www.indeed.com/viewjob?jk=52fb54968897c95b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Senior Engineer I, DevOps</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CareMetx, LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,102 +1091,102 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772f1be866124af1</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b79178087231c2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>National Computer Systems</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fb54968897c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=91ce31f9ba1d4192</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Engineer I, DevOps</t>
+          <t>Data Solutions Engineer - Hybrid / Durham, NC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CareMetx, LLC</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b79178087231c2</t>
+          <t>https://www.indeed.com/viewjob?jk=186bcafa22d4b760</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Analyst, Production Support</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Expion health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Snowflake, Time Travel, MySQL, Data Modeling</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249f623fa05a779f</t>
+          <t>https://www.indeed.com/viewjob?jk=0520916947bccd63</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - Hybrid / Durham, NC</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,112 +1221,112 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186bcafa22d4b760</t>
+          <t>https://www.indeed.com/viewjob?jk=463e1932681d1ea9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ebbo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0520916947bccd63</t>
+          <t>https://www.indeed.com/viewjob?jk=00129c0be2bb43b6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Site Reliability Engineer - GCP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Veson Nautical</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463e1932681d1ea9</t>
+          <t>https://www.indeed.com/viewjob?jk=9c626e90462e462c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ebbo</t>
+          <t>Aeroflow Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Asheville, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Glue, Athena, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,102 +1336,102 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00129c0be2bb43b6</t>
+          <t>https://www.indeed.com/viewjob?jk=0f42e6032e2d13cb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - GCP</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Veson Nautical</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c626e90462e462c</t>
+          <t>https://www.indeed.com/viewjob?jk=b83169a97751389a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>isolved</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b45e4d16b1cb423</t>
+          <t>https://www.indeed.com/viewjob?jk=b48caf12e9a2d919</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026016 - Software Engineer II (CA)</t>
+          <t>Automation QA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Moline, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, Spark, PostgreSQL, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f2f62beea8bb80a</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ffd4fd4d17a66c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Trading Analytics Developer, Quantitative Trading</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CRYPTO.com</t>
+          <t>Moderna</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, MongoDB, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfb2225c982e0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7d1fd9de87775b12</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Trading Analytics Developer, Quantitative Trading</t>
+          <t>Data Platform Engineer (Associate)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CRYPTO.com</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, MongoDB, ETL, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be62e17c354b320c</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7fc7e8196397da</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Trading Analytics Developer, Quantitative Trading</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CRYPTO.com</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, MongoDB, ETL, CI/CD</t>
+          <t>AWS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c35d0114447fb50</t>
+          <t>https://www.indeed.com/viewjob?jk=c06a4bf8bf5eacf5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Cloud Data Engineer(Korean Bilingual)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aeroflow Health</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f42e6032e2d13cb</t>
+          <t>https://www.indeed.com/viewjob?jk=82fc88c444cdb59a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>MS Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Ovation Healthcare</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Welcome, SC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,102 +1616,102 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83169a97751389a</t>
+          <t>https://www.indeed.com/viewjob?jk=fa9cfdf9043d0f23</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kubernetes Platform &amp; DevOps Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Aligned Data Centers</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morgantown, WV, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Kafka, PostgreSQL, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Kinesis, Athena, S3, RDS, Azure, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82adbdad85a792ab</t>
+          <t>https://www.indeed.com/viewjob?jk=da2322fc8a33bd97</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Full Stack Engineer, Platform Services</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>College Board</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b48caf12e9a2d919</t>
+          <t>https://www.indeed.com/viewjob?jk=b325145434e13d25</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Moderna</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1fd9de87775b12</t>
+          <t>https://www.indeed.com/viewjob?jk=70157732c8210316</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Automation QA</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ffd4fd4d17a66c</t>
+          <t>https://www.indeed.com/viewjob?jk=c4c2403873b5face</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer, Solution Test-IQ Platform</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51b37e2194c538e3</t>
+          <t>https://www.indeed.com/viewjob?jk=79b7247de0da89be</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Associate)</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7fc7e8196397da</t>
+          <t>https://www.indeed.com/viewjob?jk=2d42517f4a6ea31f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06a4bf8bf5eacf5</t>
+          <t>https://www.indeed.com/viewjob?jk=3573213c6763fded</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Azure Cloud Data Engineer(Korean Bilingual)</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82fc88c444cdb59a</t>
+          <t>https://www.indeed.com/viewjob?jk=ae6deb5151a171c2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MS Fabric Data Engineer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ovation Healthcare</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Welcome, SC, US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9cfdf9043d0f23</t>
+          <t>https://www.indeed.com/viewjob?jk=6c9b376252505568</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Databricks Data Engineer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4722e19a4c6bc57</t>
+          <t>https://www.indeed.com/viewjob?jk=283361b16a1ebc55</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JELLYFISH</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37ccdf3a9f7e654a</t>
+          <t>https://www.indeed.com/viewjob?jk=5cbd383a79d4cbef</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Full Stack Engineer, Platform Services</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>College Board</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b325145434e13d25</t>
+          <t>https://www.indeed.com/viewjob?jk=80f223b258887bd4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Forward Deployed AI/ML Engineer IV</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191a5d619c9740cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4930899ea4c30eec</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c2403873b5face</t>
+          <t>https://www.indeed.com/viewjob?jk=82199ed24d8bff3e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70157732c8210316</t>
+          <t>https://www.indeed.com/viewjob?jk=a609ef484a70728b</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b7247de0da89be</t>
+          <t>https://www.indeed.com/viewjob?jk=d315fdda0e904f4c</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d42517f4a6ea31f</t>
+          <t>https://www.indeed.com/viewjob?jk=63df87d110e211fc</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3573213c6763fded</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0e3854fb6006e0</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae6deb5151a171c2</t>
+          <t>https://www.indeed.com/viewjob?jk=269532a3a9e4d5a7</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c9b376252505568</t>
+          <t>https://www.indeed.com/viewjob?jk=5dd9ebe802598879</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283361b16a1ebc55</t>
+          <t>https://www.indeed.com/viewjob?jk=54e3579b3828b4cb</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cbd383a79d4cbef</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1cce3fa4d089a8</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f223b258887bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdfa4a99cf1b0e</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4930899ea4c30eec</t>
+          <t>https://www.indeed.com/viewjob?jk=a3cd1e1f07261faf</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82199ed24d8bff3e</t>
+          <t>https://www.indeed.com/viewjob?jk=2de2979f66f2e58c</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a609ef484a70728b</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc4c1c460908c45</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d315fdda0e904f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=a881072cca7866f9</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63df87d110e211fc</t>
+          <t>https://www.indeed.com/viewjob?jk=13bc0d51ec16f366</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0e3854fb6006e0</t>
+          <t>https://www.indeed.com/viewjob?jk=8840753fb3651a4b</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=269532a3a9e4d5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=f63908830628ad26</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dd9ebe802598879</t>
+          <t>https://www.indeed.com/viewjob?jk=a06bbcb4a7c85812</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e3579b3828b4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e1a7faad10c09b</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1cce3fa4d089a8</t>
+          <t>https://www.indeed.com/viewjob?jk=a5df440725468089</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdfa4a99cf1b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=72ebc749f6a1d990</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3cd1e1f07261faf</t>
+          <t>https://www.indeed.com/viewjob?jk=b631015d13883564</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de2979f66f2e58c</t>
+          <t>https://www.indeed.com/viewjob?jk=18dc70138cc32ac9</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc4c1c460908c45</t>
+          <t>https://www.indeed.com/viewjob?jk=f6820c1cf060fe46</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a881072cca7866f9</t>
+          <t>https://www.indeed.com/viewjob?jk=f85824dce6929812</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bc0d51ec16f366</t>
+          <t>https://www.indeed.com/viewjob?jk=dd89770faca6190f</t>
         </is>
       </c>
     </row>
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8840753fb3651a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9109da232a7f8d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Nextech</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Melbourne, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f63908830628ad26</t>
+          <t>https://www.indeed.com/viewjob?jk=f95554a6b8bcb269</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Forward Deployed AI/ML Engineer IV</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,242 +3086,242 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a06bbcb4a7c85812</t>
+          <t>https://www.indeed.com/viewjob?jk=191a5d619c9740cd</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Git, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e1a7faad10c09b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef4a72b86d37bff3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Git, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5df440725468089</t>
+          <t>https://www.indeed.com/viewjob?jk=00a98a2d8c15d1a0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Git, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72ebc749f6a1d990</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8181787c8461d9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Platform Engineer III</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Sinch</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, DynamoDB, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b631015d13883564</t>
+          <t>https://www.indeed.com/viewjob?jk=cc06fce927a41534</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18dc70138cc32ac9</t>
+          <t>https://www.indeed.com/viewjob?jk=3504f95af705a178</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Data Engineer-2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6820c1cf060fe46</t>
+          <t>https://www.indeed.com/viewjob?jk=adbfd73d28e687c7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85824dce6929812</t>
+          <t>https://www.indeed.com/viewjob?jk=0409e471c2849f2d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior AWS Connect Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd89770faca6190f</t>
+          <t>https://www.indeed.com/viewjob?jk=ace77f8600c9c3a1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior AWS Connect Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9109da232a7f8d</t>
+          <t>https://www.indeed.com/viewjob?jk=37fb83e9052e8c4f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Platform Engineer III</t>
+          <t>Cloud Engineer- Data/AI Focused</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sinch</t>
+          <t>Innovative Solutions</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, DynamoDB, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc06fce927a41534</t>
+          <t>https://www.indeed.com/viewjob?jk=33e08a12c76721e4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Engineer - Full Stack Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>Innovative Solutions</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3504f95af705a178</t>
+          <t>https://www.indeed.com/viewjob?jk=06271d579eb6e429</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer-2</t>
+          <t>Sr. Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Scala, Kafka, Snowflake, Data Modeling, dbt, MLOps, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbfd73d28e687c7</t>
+          <t>https://www.indeed.com/viewjob?jk=aec8c83533c1022a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Senior Stardog Admin/DevOps Consultant</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Cloud Storage, Scala, SQL Server, PostgreSQL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0409e471c2849f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=66fe2f823196d7aa</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior AWS Connect Engineer</t>
+          <t>SQL Server DBA</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace77f8600c9c3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=2342678cabeb9fcd</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior AWS Connect Engineer</t>
+          <t>SQL Server DBA</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37fb83e9052e8c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea93dcbac7e86e9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cloud Engineer- Data/AI Focused</t>
+          <t>SQL Server DBA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Innovative Solutions</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Scala, DynamoDB</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e08a12c76721e4</t>
+          <t>https://www.indeed.com/viewjob?jk=628c74eaec435595</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Full Stack Developer</t>
+          <t>Data Architect, Enterprise Data Platform</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Innovative Solutions</t>
+          <t>The J. M. Smucker Company</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orrville, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, Dimension Tables, Tableau</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06271d579eb6e429</t>
+          <t>https://www.indeed.com/viewjob?jk=8264f5518d85c62b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Stardog Admin/DevOps Consultant</t>
+          <t>Stardog Admin</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66fe2f823196d7aa</t>
+          <t>https://www.indeed.com/viewjob?jk=13a16d396aacef30</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SQL Server DBA</t>
+          <t>Data Scientist &amp; Machine Learning Engineer (Bellevue, Denver or LA)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Identity Digital</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
+          <t>AWS, Databricks, GCP, BigQuery, Polars, Snowflake, MLOps, MLflow, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2342678cabeb9fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c697474cdd2518</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SQL Server DBA</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea93dcbac7e86e9</t>
+          <t>https://www.indeed.com/viewjob?jk=788fc3c0ac9b4619</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SQL Server DBA</t>
+          <t>Software Engineer II- Eng</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,24 +3811,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=628c74eaec435595</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1fc3f1de5d21dc</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Stardog Admin</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Cloud Storage, Scala, SQL Server, PostgreSQL, ELT, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, MongoDB, Azure Cosmos DB, NoSQL, ETL, Azure DevOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a16d396aacef30</t>
+          <t>https://www.indeed.com/viewjob?jk=45ee9b464c973901</t>
         </is>
       </c>
     </row>
@@ -3898,25 +3898,25 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2027 Capital Markets, Quantitative Technology Services Summer Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,102 +3926,102 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb88e40dcb32f72</t>
+          <t>https://www.indeed.com/viewjob?jk=e06d6e56ef7c81de</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788fc3c0ac9b4619</t>
+          <t>https://www.indeed.com/viewjob?jk=6629a97b773e9046</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer II- Eng</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1fc3f1de5d21dc</t>
+          <t>https://www.indeed.com/viewjob?jk=bd21fd4293097f4d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Quest Analytics Internship Program - Summer 2027 in Kansas City</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Quest Analytics</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Databricks, Spark, SQL Server, MongoDB, NoSQL, ETL, ELT, Power BI, Git, Python</t>
+          <t>Google Cloud Platform, Hadoop, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa096b5f07acc65b</t>
+          <t>https://www.indeed.com/viewjob?jk=11f86cdd4c675439</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Senior Workday Financials Integration Developer (Consultant)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AG Consulting Partners</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, MongoDB, Azure Cosmos DB, NoSQL, ETL, Azure DevOps</t>
+          <t>RDS, Azure, Scala, ETL, ELT, Power BI, Tableau, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ee9b464c973901</t>
+          <t>https://www.indeed.com/viewjob?jk=57f5ec07c77f1adc</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
+          <t>AWS, ECS, RDS, Azure, Kafka, SQL Server, PostgreSQL, MongoDB, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06d6e56ef7c81de</t>
+          <t>https://www.indeed.com/viewjob?jk=1200afb16be7a459</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SquareTrade</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0a62a40f8906c0</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7802e0b1c362ab</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer – Enterprise Applications</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Allen Control Systems</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6629a97b773e9046</t>
+          <t>https://www.indeed.com/viewjob?jk=eaff489ad3919834</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,67 +4206,67 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd21fd4293097f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=b320160e6257e21f</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Hadoop, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, Snowflake, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11f86cdd4c675439</t>
+          <t>https://www.indeed.com/viewjob?jk=39e8077574f9d2d1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer III - Enterprise Intelligence</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EarnIn</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,67 +4276,67 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f20f480a6626da</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3f3c53f35b1893</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Technology Development Program Associate - August 2027</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7802e0b1c362ab</t>
+          <t>https://www.indeed.com/viewjob?jk=718fa3c3e4a98b95</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Database Administrator - PostgreSQL Carmel, United States Sep. 15, 2026</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Alter Domus</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=466ef9cc01d7f367</t>
+          <t>https://www.indeed.com/viewjob?jk=b50e5db3bf7a0090</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Enterprise AI Systems Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Kafka, SQL Server, PostgreSQL, MongoDB, Cassandra, CI/CD</t>
+          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1200afb16be7a459</t>
+          <t>https://www.indeed.com/viewjob?jk=90542e98749e2837</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer – Enterprise Applications</t>
+          <t>Enterprise AI Systems Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Allen Control Systems</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaff489ad3919834</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba67ab5bc7e4a04</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Enterprise AI Systems Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b320160e6257e21f</t>
+          <t>https://www.indeed.com/viewjob?jk=fe935e70dd3f2e18</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Enterprise AI Systems Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, MongoDB, Data Modeling, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,59 +4486,59 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d430b11f1930cc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=037741e66967443c</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Associate Architects</t>
+          <t>Senior Calypso Java Developer Consultant</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Merck KGaA</t>
+          <t>Tekserv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Spark, Scala, Oracle, SQL Server, PostgreSQL, Cassandra, NoSQL, CI/CD, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, MLOps, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58202f48c352ef63</t>
+          <t>https://www.indeed.com/viewjob?jk=8359a4f919eb2d99</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Calypso Java Developer Consultant</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>Tekserv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, Snowflake, NoSQL, ETL</t>
+          <t>AWS, Azure, Scala, Oracle, Data Modeling, ETL, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e8077574f9d2d1</t>
+          <t>https://www.indeed.com/viewjob?jk=89ff0cd4686bfd2e</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer III - Enterprise Intelligence</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3f3c53f35b1893</t>
+          <t>https://www.indeed.com/viewjob?jk=5a86278bda2e3b90</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist Intern</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Westchester, IL, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e1b18d9ff34a767</t>
+          <t>https://www.indeed.com/viewjob?jk=af8c2d05083f261a</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist Intern</t>
+          <t>Senior Software Engineer – Manufacturing Digital Operations</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Westchester, IL, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, Data Modeling, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222cf2907d848f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c17d5756834ac8</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Engineer, AI Enablement</t>
+          <t>Senior LLMOps Engineer, Development</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59419b9909aa5e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=1698a3db62a44dc8</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Smarsh</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,472 +4721,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Hive, Scala, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991793b1299304ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Technology Development Program Associate - August 2027</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=718fa3c3e4a98b95</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Encore Global</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Schiller Park, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da71cda8fc390157</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b50e5db3bf7a0090</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Enterprise AI Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>JUUL Labs</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90542e98749e2837</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Enterprise AI Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>JUUL Labs</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba67ab5bc7e4a04</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Enterprise AI Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>JUUL Labs</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe935e70dd3f2e18</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Enterprise AI Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>JUUL Labs</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, GCP, Vertex AI, Scala, Splunk, CI/CD, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=037741e66967443c</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Data Engineering Intern</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>CAI (Computer Aid, Inc.)</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=448bed8907ce0072</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Trimble</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Lake Oswego, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af8c2d05083f261a</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer – Manufacturing Digital Operations</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Warren, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, Data Modeling, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c17d5756834ac8</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Senior LLMOps Engineer, Development</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Citrin Cooperman Advisors LLC</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1698a3db62a44dc8</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>BI Report Developer</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Topgolf</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, RDS, Azure, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b493a51345446a14</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Qualys Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>UltraViolet Cyber</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, ELT, REST API integration, Splunk, Python</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1967e3fb659eb2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ec12045d23a841</t>
         </is>
       </c>
     </row>
